--- a/backend/app/data/oficial/01_carga_oficial_catalogos_v3.xlsx
+++ b/backend/app/data/oficial/01_carga_oficial_catalogos_v3.xlsx
@@ -5264,12 +5264,12 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
-          <t>FOOTWEAR (secondary), APPAREL (secondary)</t>
+          <t>RAW_MATERIALS, FOOTWEAR (secondary), APPAREL (secondary)</t>
         </is>
       </c>
       <c r="J59" s="10" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="I60" s="10" t="inlineStr">
         <is>
-          <t>FOOTWEAR (secondary), APPAREL (secondary)</t>
+          <t>RAW_MATERIALS, FOOTWEAR (secondary), APPAREL (secondary)</t>
         </is>
       </c>
       <c r="J60" s="10" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
-          <t>FOOTWEAR (secondary), APPAREL (secondary)</t>
+          <t>RAW_MATERIALS, FOOTWEAR (secondary), APPAREL (secondary)</t>
         </is>
       </c>
       <c r="J61" s="10" t="inlineStr">
@@ -14418,7 +14418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14452,3327 +14452,6 @@
       <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Purpose</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>RAW_MATERIALS</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>FOOTWEAR</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D80" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D82" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>APPAREL</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D84" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D89" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D90" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D92" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E93" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D94" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D96" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E96" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C98" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E98" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D99" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E100" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E101" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E102" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D104" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E104" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>Automatic candidate domain mapping; does not override legal notes or official tariff text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E106" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B107" s="10" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E107" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E108" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E110" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E112" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C114" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D114" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E114" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D115" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D116" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E116" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E120" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C122" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E122" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E123" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>ACCESSORIES_MERCH</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E124" s="10" t="inlineStr">
-        <is>
-          <t>Available as related/manual candidate when product attributes justify it.</t>
         </is>
       </c>
     </row>
